--- a/data/trans_orig/IP07C11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>51007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32900</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37142</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56456</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21303</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44346</t>
+          <t>43722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58812</t>
+          <t>58734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49160</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62647</t>
+          <t>61984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97414</t>
+          <t>97364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117528</t>
+          <t>117759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61669</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46571</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>60466</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25763</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>45564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50133</t>
+          <t>50189</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>150607</t>
+          <t>149775</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>175963</t>
+          <t>176192</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>177808</t>
+          <t>176241</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>202797</t>
+          <t>203120</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>334260</t>
+          <t>333787</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>370787</t>
+          <t>371358</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>77500</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>101542</t>
+          <t>102339</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>76183</t>
+          <t>76900</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>100890</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>161011</t>
+          <t>160423</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>197714</t>
+          <t>198058</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>32384</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28857</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52911</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37015</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>48661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>57709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71904</t>
+          <t>72215</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110526</t>
+          <t>110201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>131326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>32137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37017</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44045</t>
+          <t>44351</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>64522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43832</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57009</t>
+          <t>56712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82733</t>
+          <t>83103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101903</t>
+          <t>102387</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32356</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41270</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33390</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45237</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>177296</t>
+          <t>176257</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>204629</t>
+          <t>204837</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>185857</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>212611</t>
+          <t>212356</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>370732</t>
+          <t>368797</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>409745</t>
+          <t>407024</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>83026</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>110174</t>
+          <t>110077</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>108761</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>172690</t>
+          <t>174233</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>209374</t>
+          <t>210775</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39265</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>52268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68112</t>
+          <t>67451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>65554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81922</t>
+          <t>82997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>69244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125474</t>
+          <t>124936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147807</t>
+          <t>147167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39266</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>50260</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70715</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75097</t>
+          <t>74123</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94351</t>
+          <t>94793</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>41926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>61454</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30379</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36385</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>187947</t>
+          <t>186649</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>216384</t>
+          <t>217310</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>196537</t>
+          <t>198363</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>227671</t>
+          <t>226769</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>393995</t>
+          <t>393931</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>433540</t>
+          <t>433933</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89932</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>117225</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>88867</t>
+          <t>90393</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>117822</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>189460</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>228064</t>
+          <t>227136</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>43222</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
